--- a/Producao/Modelos/PROGRAMACAO_PROGRAMACAO_MODELO.xlsx
+++ b/Producao/Modelos/PROGRAMACAO_PROGRAMACAO_MODELO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CIPOLATTI\SISTEMAS\Producao\Producao\Modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Codex\2026-05-21\clona-o-repositorio-wognascimento-financeiro-git\Producao\Producao\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE61F7C-E239-4D9A-93A7-6D0B62935218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245D6261-B66C-4BBE-9025-89F58C736FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-15" windowWidth="38640" windowHeight="15720" xr2:uid="{D9A668C6-916A-46D2-B14A-67ECE735CF5F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{D9A668C6-916A-46D2-B14A-67ECE735CF5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>PROGRAMAÇÃO DE PRODUÇÃO</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>META HT</t>
+  </si>
+  <si>
+    <t>TIPO</t>
   </si>
 </sst>
 </file>
@@ -232,32 +235,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B133AB98-A64E-4483-B00B-7C9E9882B78B}">
-  <dimension ref="B1:T8"/>
+  <dimension ref="B1:U8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -595,132 +598,132 @@
     <col min="20" max="20" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
+    <row r="1" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="5"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="10"/>
       <c r="N3" s="1">
         <f>COUNTIF(N9:N1048576,"FILA/M.O")</f>
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="5"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="10"/>
       <c r="R3" s="1">
         <f>COUNTIF(N9:N1048576,"INDEFINIDO")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="4" t="s">
+      <c r="G4" s="10"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="10"/>
       <c r="N4" s="1">
         <f>COUNTIF(N9:N1048576,"EM ANDAMENTO")</f>
         <v>0</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="5"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="10"/>
       <c r="R4" s="1">
         <f>COUNTIF(N9:N1048576,"PROJETOS")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="4" t="s">
+      <c r="G5" s="10"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="5"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="10"/>
       <c r="N5" s="1">
         <f>COUNTIF(N9:N1048576,"EMBALAGEM/EXPEDIÇÃO")</f>
         <v>0</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="5"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="10"/>
       <c r="R5" s="1">
         <f>COUNTIF(N9:N1048576,"FALTA MATERIAL INTERNO / TRANSF")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="5"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="10"/>
       <c r="N6" s="1">
         <f>COUNTIF(N9:N1048576,"ESPAÇO FÍSICO")</f>
         <v>0</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="5"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="10"/>
       <c r="R6" s="1">
         <f>COUNTIF(N9:N1048576,"FALTA MATERIAL EXTERNO / COMPRAS")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
@@ -736,44 +739,40 @@
       <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="7"/>
       <c r="M8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="10" t="s">
+      <c r="P8" s="7"/>
+      <c r="Q8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R8" s="11"/>
+      <c r="R8" s="7"/>
       <c r="S8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:J5"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="O4:Q4"/>
@@ -783,6 +782,13 @@
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
